--- a/data/raw/inventory/Week 27/White_Mulberry/Inventory Snapshot.xlsx
+++ b/data/raw/inventory/Week 27/White_Mulberry/Inventory Snapshot.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12.88671875" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -2050,7 +2050,36 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1"/>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FBA79476</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>WM-GS1M-BK</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>357</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
+    </row>
     <row r="43" ht="15" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:L41"/>
